--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task3_question_quality.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task3_question_quality.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0899AE5-902B-43B3-AD35-8F98C7CD847E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AB8852-2593-43D8-95E7-9B8E8CC12167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="157">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +69,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000132-0003</t>
-  </si>
-  <si>
-    <t>I'm considering an adventure trip to Patagonia.</t>
-  </si>
-  <si>
-    <t>Have you researched the logistics of the trip?</t>
-  </si>
-  <si>
-    <t>Have you looked into tour operators for the trip?</t>
-  </si>
-  <si>
-    <t>Have you planned the details of your trip?</t>
-  </si>
-  <si>
-    <t>Have you started planning for the trip?</t>
-  </si>
-  <si>
-    <t>Have you started planning your Patagonia adventure?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000107-0003</t>
-  </si>
-  <si>
-    <t>It's so cloudy out, I don't even want to leave my house.</t>
-  </si>
-  <si>
-    <t>Do you have any favorite movies you like to watch on a rainy day?</t>
-  </si>
-  <si>
-    <t>Do you have any upcoming plans for the weekend?</t>
-  </si>
-  <si>
-    <t>Do you have any fun plans coming up?</t>
-  </si>
-  <si>
-    <t>What's your favorite movie?</t>
-  </si>
-  <si>
-    <t>Have you tried any new restaurants lately?</t>
+    <t>SFTANNO-000077-0003</t>
+  </si>
+  <si>
+    <t>I didn't know there were so many different regions and cultures in Japan.</t>
+  </si>
+  <si>
+    <t>Have you researched which regions you want to visit?</t>
+  </si>
+  <si>
+    <t>Have you considered visiting different regions during your trip?</t>
+  </si>
+  <si>
+    <t>Have you looked into any specific regions or cities you want to visit?</t>
+  </si>
+  <si>
+    <t>Which regions are you planning to visit?</t>
+  </si>
+  <si>
+    <t>Do you have any specific places you want to visit in Japan?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000153-0003</t>
+  </si>
+  <si>
+    <t>I'm worried my scrapbook won't be as good as some of the ones I've seen online.</t>
+  </si>
+  <si>
+    <t>Have you considered adding your own personal touch to the design?</t>
+  </si>
+  <si>
+    <t>What kind of materials or embellishments are you planning on using?</t>
+  </si>
+  <si>
+    <t>Have you considered any unique embellishments or materials you could add?</t>
+  </si>
+  <si>
+    <t>Have you thought about what type of scrapbooking supplies you want to use?</t>
+  </si>
+  <si>
+    <t>What's your favorite memory from last summer that you're hoping to include in your scrapbook?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0003</t>
@@ -161,214 +174,208 @@
     <t>Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000094-0003</t>
-  </si>
-  <si>
-    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
+    <t>SFTANNO-000131-0003</t>
+  </si>
+  <si>
+    <t>I've always dreamed of visiting Japan, but I'm afraid of the language barrier.</t>
+  </si>
+  <si>
+    <t>Have you considered learning some basic Japanese phrases?</t>
+  </si>
+  <si>
+    <t>Have you looked into any cultural exchange programs?</t>
+  </si>
+  <si>
+    <t>Any other destinations you're interested in?</t>
+  </si>
+  <si>
+    <t>Have you started planning your itinerary?</t>
+  </si>
+  <si>
+    <t>Have you researched any cultural experiences you'd like to have?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000058-0003</t>
+  </si>
+  <si>
+    <t>I heard a rumor that the COVID-19 vaccine makes you infertile, is that true?</t>
+  </si>
+  <si>
+    <t>How can we help people separate fact from fiction?</t>
+  </si>
+  <si>
+    <t>Where did you hear that rumor?</t>
+  </si>
+  <si>
+    <t>Do you have any other questions about the vaccine?</t>
+  </si>
+  <si>
+    <t>Do you have any tips on how to combat misinformation?</t>
+  </si>
+  <si>
+    <t>Have you considered getting vaccinated?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000025-0003</t>
+  </si>
+  <si>
+    <t>I feel a bit better about it. Maybe I'll try talking to them again.</t>
+  </si>
+  <si>
+    <t>Do you want any support while you talk to them?</t>
+  </si>
+  <si>
+    <t>Do you need any help preparing for the conversation?</t>
+  </si>
+  <si>
+    <t>Do you want to talk more about it after you have the conversation?</t>
+  </si>
+  <si>
+    <t>Is there anything else you want to talk about?</t>
+  </si>
+  <si>
+    <t>Do you have any other concerns or questions?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000098-0003</t>
+  </si>
+  <si>
+    <t>Have you ever ridden in an autonomous vehicle before?</t>
+  </si>
+  <si>
+    <t>Do you think you would be interested in taking a ride in one sometime?</t>
+  </si>
+  <si>
+    <t>Would you be open to trying it out sometime?</t>
+  </si>
+  <si>
+    <t>Have you ever tried any other autonomous technologies, like self-driving cars?</t>
+  </si>
+  <si>
+    <t>What do you think it would be like to ride in an autonomous vehicle?</t>
+  </si>
+  <si>
+    <t>Would you be interested in trying one out?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000050-0003</t>
+  </si>
+  <si>
+    <t>I'm open to anything at this point.</t>
+  </si>
+  <si>
+    <t>Have you thought about any specific companies you'd like to work for?</t>
+  </si>
+  <si>
+    <t>Have you thought about reaching out to any recruiters?</t>
+  </si>
+  <si>
+    <t>Have you thought about reaching out to any old colleagues or contacts for job leads?</t>
+  </si>
+  <si>
+    <t>Have you looked into any job boards or websites?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000078-0003</t>
+  </si>
+  <si>
+    <t>I'm worried about cultural misunderstandings when I visit my parents' homeland.</t>
+  </si>
+  <si>
+    <t>That's a great idea! What phrases or customs have you looked into so far?</t>
+  </si>
+  <si>
+    <t>Have you looked into any cultural exchange programs or language courses that could help you better understand the local culture?</t>
+  </si>
+  <si>
+    <t>Have you researched any cultural etiquette or customs that you should be aware of before your trip?</t>
+  </si>
+  <si>
+    <t>Have you looked into any language courses or resources to help with communication while traveling?</t>
+  </si>
+  <si>
+    <t>What are some specific things you're looking forward to experiencing in your parents' homeland?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000095-0003</t>
+  </si>
+  <si>
+    <t>Yes, I have. I was so frustrated that the seat was uncomfortable and the entertainment system was broken.</t>
   </si>
   <si>
     <t>Do you have any tips for avoiding jet lag?</t>
   </si>
   <si>
-    <t>Do you have any travel hacks or tips you like to use?</t>
-  </si>
-  <si>
-    <t>Have you ever met someone interesting on a flight?</t>
-  </si>
-  <si>
-    <t>What's your favorite travel destination?</t>
-  </si>
-  <si>
-    <t>Do you have any travel hacks or tips?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000103-0003</t>
-  </si>
-  <si>
-    <t>I've been browsing, but I don't want to compromise on quality either.</t>
-  </si>
-  <si>
-    <t>Do you have any favorite VR games or experiences?</t>
-  </si>
-  <si>
-    <t>Have you considered waiting for a sale or promotion on the VR headset you want?</t>
-  </si>
-  <si>
-    <t>Have you considered saving up or waiting for sales?</t>
-  </si>
-  <si>
-    <t>Have you considered waiting for a sale or discount?</t>
-  </si>
-  <si>
-    <t>Have you considered any other alternatives or options?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000025-0003</t>
-  </si>
-  <si>
-    <t>I feel a bit better about it. Maybe I'll try talking to them again.</t>
-  </si>
-  <si>
-    <t>Do you want any support while you talk to them?</t>
-  </si>
-  <si>
-    <t>Do you need any help preparing for the conversation?</t>
-  </si>
-  <si>
-    <t>Do you want to talk more about it after you have the conversation?</t>
-  </si>
-  <si>
-    <t>Is there anything else you want to talk about?</t>
-  </si>
-  <si>
-    <t>Do you have any other concerns or questions?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000064-0003</t>
-  </si>
-  <si>
-    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
-  </si>
-  <si>
-    <t>What local organizations do you know of that are promoting change?</t>
-  </si>
-  <si>
-    <t>What local organizations do you recommend we reach out to?</t>
-  </si>
-  <si>
-    <t>What local organizations do you think we should start with?</t>
-  </si>
-  <si>
-    <t>What organizations do you suggest we reach out to?</t>
-  </si>
-  <si>
-    <t>How do you suggest we use social media to spread awareness?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000145-0003</t>
-  </si>
-  <si>
-    <t>That's a great idea! I hadn't thought about that.</t>
-  </si>
-  <si>
-    <t>Do you have any other ideas for making sustainable changes?</t>
-  </si>
-  <si>
-    <t>What other sustainability changes are you thinking about making?</t>
-  </si>
-  <si>
-    <t>What other changes do you want to make in your daily life?</t>
-  </si>
-  <si>
-    <t>Do you have any other sustainability tips or ideas you'd like to share?</t>
-  </si>
-  <si>
-    <t>Have you considered supporting sustainable fashion brands?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000152-0003</t>
-  </si>
-  <si>
-    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
-  </si>
-  <si>
-    <t>Have you considered taking a class to get some hands-on experience?</t>
-  </si>
-  <si>
-    <t>What kind of project are you thinking about making?</t>
-  </si>
-  <si>
-    <t>Have you thought about starting with a simple design and building from there?</t>
-  </si>
-  <si>
-    <t>Have you thought about taking a class to learn some techniques?</t>
-  </si>
-  <si>
-    <t>What kind of scrapbooking materials do you like to use?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000159-0003</t>
-  </si>
-  <si>
-    <t>We should start by setting some ground rules for respectful discussion.</t>
-  </si>
-  <si>
-    <t>How do we create these rules?</t>
-  </si>
-  <si>
-    <t>How can we ensure we follow these rules?</t>
-  </si>
-  <si>
-    <t>What rules do you suggest?</t>
-  </si>
-  <si>
-    <t>What rules do you suggest we implement?</t>
-  </si>
-  <si>
-    <t>What other steps can we take?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000096-0003</t>
-  </si>
-  <si>
-    <t>I missed the last train, and I'm stuck in the city.</t>
-  </si>
-  <si>
-    <t>Is there anything I can do to help you?</t>
-  </si>
-  <si>
-    <t>I'll help you find one if you need it.</t>
-  </si>
-  <si>
-    <t>Do you need help finding a nearby hotel or shelter?</t>
-  </si>
-  <si>
-    <t>Do you have any friends or contacts in the area?</t>
-  </si>
-  <si>
-    <t>Can I help you find a taxi or other transportation option?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000089-0003</t>
-  </si>
-  <si>
-    <t>They have a really solid defense and excellent ball control.</t>
-  </si>
-  <si>
-    <t>Do you have a favorite soccer player?</t>
-  </si>
-  <si>
-    <t>Do you have any upcoming soccer games you're looking forward to?</t>
-  </si>
-  <si>
-    <t>Do you have any other teams you like to watch?</t>
-  </si>
-  <si>
-    <t>Who do you think is the best player on FC Barcelona?</t>
-  </si>
-  <si>
-    <t>Have you ever been to a live soccer game?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000135-0003</t>
-  </si>
-  <si>
-    <t>I did a river rafting trip once, but the water was so dirty.</t>
-  </si>
-  <si>
-    <t>Have you tried any other outdoor adventures?</t>
-  </si>
-  <si>
-    <t>Have you ever tried whitewater rafting in a clean river?</t>
-  </si>
-  <si>
-    <t>Have you ever tried any adventure sports that involve water?</t>
-  </si>
-  <si>
-    <t>Have you gone rafting on a cleaner river since then?</t>
-  </si>
-  <si>
-    <t>Have you ever gone on a clean and safe river rafting trip?</t>
+    <t>Have you ever tried any in-flight movies that you really enjoyed?</t>
+  </si>
+  <si>
+    <t>Have you ever flown with a layover?</t>
+  </si>
+  <si>
+    <t>Do you have any tips for surviving long-haul flights?</t>
+  </si>
+  <si>
+    <t>Do you prefer window or aisle seats?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000139-0003</t>
+  </si>
+  <si>
+    <t>I'm scared my children are spending too much time online.</t>
+  </si>
+  <si>
+    <t>Have you talked to your children about online safety?</t>
+  </si>
+  <si>
+    <t>Have you talked to them about online safety?</t>
+  </si>
+  <si>
+    <t>Have you talked to your kids about online safety and how to avoid dangers?</t>
+  </si>
+  <si>
+    <t>Have you considered setting up parental controls or online monitoring software?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000130-0003</t>
+  </si>
+  <si>
+    <t>One episode covered the injustices faced by indigenous communities in regard to traditional plant knowledge and genetics research.</t>
+  </si>
+  <si>
+    <t>Have you found any other resources that cover the intersection of plant genetics and social justice?</t>
+  </si>
+  <si>
+    <t>Do you have any recommendations for other podcasts or resources that cover similar topics?</t>
+  </si>
+  <si>
+    <t>What do you think can be done to improve the representation of indigenous voices in plant genetics research?</t>
+  </si>
+  <si>
+    <t>Do you know of any organizations that are working towards these goals?</t>
+  </si>
+  <si>
+    <t>What other topics do you think the podcast should cover?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000073-0003</t>
+  </si>
+  <si>
+    <t>I saw a video of a robot dancing and it was just strange to watch.</t>
+  </si>
+  <si>
+    <t>Do you think robots will ever be able to perfectly replicate human movement?</t>
+  </si>
+  <si>
+    <t>What other areas of our lives do you think robots could potentially take over?</t>
+  </si>
+  <si>
+    <t>Do you think robots could ever replicate the emotional connection we have with dance?</t>
+  </si>
+  <si>
+    <t>Do you think there should be regulations put in place for robots and their capabilities?</t>
+  </si>
+  <si>
+    <t>Have you ever interacted with a robot before?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0003</t>
@@ -389,46 +396,46 @@
     <t>Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000163-0003</t>
-  </si>
-  <si>
-    <t>I wish I could go back in time to see history up close.</t>
-  </si>
-  <si>
-    <t>What historical event would you like to witness if you could?</t>
-  </si>
-  <si>
-    <t>Have you ever visited any historical sites?</t>
-  </si>
-  <si>
-    <t>Have you ever read a book about a historical event?</t>
-  </si>
-  <si>
-    <t>It's important to appreciate history as it is, not just wish we could change it.</t>
-  </si>
-  <si>
-    <t>It's always important to appreciate and learn from the past.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000102-0003</t>
-  </si>
-  <si>
-    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
-  </si>
-  <si>
-    <t>Have you tried playing any other Pokemon games in the meantime?</t>
-  </si>
-  <si>
-    <t>Have you tried playing any of the older Pokemon games?</t>
-  </si>
-  <si>
-    <t>What other games have you been playing lately?</t>
-  </si>
-  <si>
-    <t>Have you considered trying a different game instead?</t>
-  </si>
-  <si>
-    <t>What other Pokemon games have you played?</t>
+    <t>SFTANNO-000105-0003</t>
+  </si>
+  <si>
+    <t>I don't like this cold and gloomy weather.</t>
+  </si>
+  <si>
+    <t>Have you tried any indoor activities to lift your spirits?</t>
+  </si>
+  <si>
+    <t>What's your favorite thing to do on a cold day?</t>
+  </si>
+  <si>
+    <t>Have you tried any new indoor activities recently?</t>
+  </si>
+  <si>
+    <t>Have you ever tried indoor rock climbing?</t>
+  </si>
+  <si>
+    <t>What's your favorite way to spend a rainy day?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000154-0003</t>
+  </si>
+  <si>
+    <t>My partner keeps criticizing how I chop vegetables, it's driving me insane.</t>
+  </si>
+  <si>
+    <t>Have you tried watching cooking shows or reading recipes together to find a compromise?</t>
+  </si>
+  <si>
+    <t>Have you thought about trying a new recipe together?</t>
+  </si>
+  <si>
+    <t>Do you have any other cooking tips to share?</t>
+  </si>
+  <si>
+    <t>Have you tried talking to them about it?</t>
+  </si>
+  <si>
+    <t>Have you tried any new recipes lately?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0003</t>
@@ -473,25 +480,25 @@
     <t>Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000062-0003</t>
-  </si>
-  <si>
-    <t>I'm thrilled to see more young people engaging in politics.</t>
-  </si>
-  <si>
-    <t>Have you engaged with any youth activism groups?</t>
-  </si>
-  <si>
-    <t>Have you considered organizing events or workshops to encourage political participation?</t>
-  </si>
-  <si>
-    <t>Have you been following any inspiring young politicians or activists?</t>
-  </si>
-  <si>
-    <t>How do you think we can continue encouraging young people to stay engaged?</t>
-  </si>
-  <si>
-    <t>Have you considered mentoring or supporting young political activists?</t>
+    <t>SFTANNO-000118-0003</t>
+  </si>
+  <si>
+    <t>We can support local community clinics and increase our involvement in community-based programs that advocate for health equity.</t>
+  </si>
+  <si>
+    <t>What other initiatives can we support to promote health equity?</t>
+  </si>
+  <si>
+    <t>How can we continue to work towards making healthcare more accessible and equitable for all?</t>
+  </si>
+  <si>
+    <t>How can we encourage more people to get involved and support these initiatives?</t>
+  </si>
+  <si>
+    <t>What other ideas do you have to promote health equity at the local level?</t>
+  </si>
+  <si>
+    <t>What other initiatives can we take to support health equity in our communities?</t>
   </si>
 </sst>
 </file>
@@ -859,14 +866,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="2" customWidth="1"/>
-    <col min="2" max="13" width="27.33203125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="9.85546875" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.7109375" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -918,34 +925,34 @@
         <v>15</v>
       </c>
       <c r="D2" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -956,34 +963,34 @@
         <v>22</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -994,7 +1001,7 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
@@ -1006,22 +1013,22 @@
         <v>31</v>
       </c>
       <c r="H4" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1032,34 +1039,34 @@
         <v>36</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1076,28 +1083,28 @@
         <v>44</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1108,34 +1115,34 @@
         <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1146,34 +1153,34 @@
         <v>57</v>
       </c>
       <c r="D8" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1184,25 +1191,25 @@
         <v>64</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
@@ -1211,7 +1218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1222,13 +1229,13 @@
         <v>71</v>
       </c>
       <c r="D10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
@@ -1240,16 +1247,16 @@
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1260,446 +1267,446 @@
         <v>78</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="2">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="2">
-        <v>3</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2">
+        <v>3</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="2">
-        <v>2</v>
-      </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="2">
-        <v>4</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="2">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="2">
-        <v>5</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="2">
-        <v>2</v>
-      </c>
-      <c r="K14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="2">
+        <v>4</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="2">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="J15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="2">
-        <v>4</v>
-      </c>
-      <c r="I15" s="2" t="s">
+      <c r="L15" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="J16" s="2">
+        <v>4</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="2">
-        <v>2</v>
-      </c>
-      <c r="I16" s="2" t="s">
+      <c r="L16" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="2">
-        <v>4</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="H17" s="2">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="2">
-        <v>5</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="2">
-        <v>4</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="2">
-        <v>2</v>
-      </c>
-      <c r="K17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L17" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F18" s="2">
-        <v>3</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="J18" s="2">
+        <v>5</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="2">
-        <v>4</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="J18" s="2">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L18" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="H19" s="2">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="2">
-        <v>5</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="2">
-        <v>4</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="L19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J19" s="2">
-        <v>3</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="2">
-        <v>3</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="J20" s="2">
+        <v>4</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="2">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="L20" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="L20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="2">
-        <v>5</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2">
+        <v>4</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="2">
-        <v>4</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="J21" s="2">
+        <v>5</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="2">
-        <v>3</v>
-      </c>
-      <c r="K21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L21" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="H22" s="2">
+        <v>4</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F22" s="2">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="J22" s="2">
+        <v>3</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="H22" s="2">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="L22" s="2">
         <v>5</v>
@@ -1707,7 +1714,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{CF72A3CD-43BC-4566-84F7-204132638037}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{FA946230-4A95-4C9A-8787-BDC0183F1EE5}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
